--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46021.375</v>
+        <v>46021.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.75</v>
       </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="M23" t="n">
         <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="M21" t="n">
         <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.75</v>
       </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
         <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.75</v>
       </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.75</v>
       </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.75</v>
       </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.75</v>
       </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>3.73</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>3.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1141,7 +1141,7 @@
         <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="M23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.69</v>
-      </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.2</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.7</v>
       </c>
-      <c r="N14" t="n">
+      <c r="T14" t="n">
         <v>2.2</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.73</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
         <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
         <v>2.1</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.69</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3405,64 +3405,64 @@
         <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3762,40 +3762,40 @@
         <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
         <v>1.88</v>
@@ -3804,22 +3804,22 @@
         <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.19</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.7</v>
       </c>
-      <c r="N12" t="n">
+      <c r="T12" t="n">
         <v>2.2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.48</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>3.19</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.02</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.15</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.61</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.22</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.69</v>
+        <v>3.73</v>
       </c>
       <c r="O23" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>4.96</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.73</v>
+        <v>2.69</v>
       </c>
       <c r="O24" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.96</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.94</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.18</v>
-      </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
         <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
+        <v>5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH27" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.24</v>
+        <v>3.99</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -689,7 +689,7 @@
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -701,13 +701,13 @@
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.28</v>
@@ -722,7 +722,7 @@
         <v>1.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
         <v>1.74</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1620,64 +1620,64 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>3.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AG11" t="n">
         <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1864,31 +1864,31 @@
         <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.15</v>
+        <v>4.27</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
         <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
         <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
         <v>4.65</v>
@@ -1909,13 +1909,13 @@
         <v>1.59</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>3.19</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.7</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.6</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.88</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.3</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.68</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2453,40 +2453,40 @@
         <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA17" t="n">
         <v>1.85</v>
@@ -2495,22 +2495,22 @@
         <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>3.73</v>
       </c>
       <c r="O19" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.22</v>
+        <v>4.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
         <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2810,40 +2810,40 @@
         <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA20" t="n">
         <v>1.8</v>
@@ -2852,22 +2852,22 @@
         <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>2.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.05</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Q22" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.96</v>
+        <v>5.33</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3420,7 +3420,7 @@
         <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
         <v>1.43</v>
@@ -3429,7 +3429,7 @@
         <v>5.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3438,7 +3438,7 @@
         <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="AA25" t="n">
         <v>1.77</v>
@@ -3453,13 +3453,13 @@
         <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
         <v>1.18</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
         <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.92</v>
       </c>
-      <c r="AC26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.52</v>
+        <v>2.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
         <v>6.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3762,40 +3762,40 @@
         <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA28" t="n">
         <v>1.95</v>
@@ -3804,22 +3804,22 @@
         <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.6</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.02</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.27</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>4.27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3.36</v>
       </c>
       <c r="T14" t="n">
-        <v>3.19</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.05</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.46</v>
+        <v>6.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>2.64</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="P20" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.53</v>
+        <v>3.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.88</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.3</v>
       </c>
-      <c r="V21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z21" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
         <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,34 +3277,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.94</v>
+        <v>3.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.08</v>
+        <v>2.46</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
         <v>5.3</v>
@@ -3316,16 +3316,16 @@
         <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
         <v>2.49</v>
@@ -3334,16 +3334,16 @@
         <v>1.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>2.79</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AE26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.64</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.79</v>
+        <v>1.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>3.01</v>
+        <v>2.28</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>4.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.42</v>
+        <v>2.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>2.68</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
         <v>3.99</v>
@@ -683,13 +683,13 @@
         <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="U2" t="n">
         <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -701,7 +701,7 @@
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
         <v>2</v>
@@ -722,10 +722,10 @@
         <v>1.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>4.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>3.19</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>8.1</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
         <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
         <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>3.19</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.02</v>
+        <v>3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.27</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="R15" t="n">
         <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,49 +2444,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>6.1</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.53</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA17" t="n">
         <v>1.8</v>
@@ -2495,22 +2495,22 @@
         <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.64</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
         <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="T21" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.97</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.51</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>5.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="T22" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.02</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z23" t="n">
         <v>4</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
         <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.88</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.46</v>
+        <v>6.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
         <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>2.64</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.79</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>3.01</v>
+        <v>2.28</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.14</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.42</v>
+        <v>2.34</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>3.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>6.25</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.61</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
         <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="T28" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="U28" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
         <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
         <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>3.19</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.7</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.6</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>6.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.34</v>
+        <v>6.53</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>2.64</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.99</v>
+        <v>2.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>5.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2572,40 +2572,40 @@
         <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA18" t="n">
         <v>1.7</v>
@@ -2614,10 +2614,10 @@
         <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
         <v>1.85</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.88</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="N19" t="n">
-        <v>3.73</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.96</v>
+        <v>3.34</v>
       </c>
       <c r="R19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.35</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
-        <v>2.34</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.33</v>
+        <v>3.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="T22" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>3.73</v>
       </c>
       <c r="O23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.94</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.29</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.49</v>
+        <v>3.38</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.41</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.1</v>
+        <v>2.69</v>
       </c>
       <c r="O24" t="n">
-        <v>1.91</v>
+        <v>3.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.53</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.8</v>
       </c>
-      <c r="AA24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.64</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.42</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>6.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>2.61</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.63</v>
+        <v>3.01</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>6.25</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.61</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1742,13 +1742,13 @@
         <v>2.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
         <v>4.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
         <v>3.36</v>
@@ -1757,7 +1757,7 @@
         <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
         <v>4.8</v>
@@ -1793,10 +1793,10 @@
         <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.26</v>
+        <v>2.92</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1980,31 +1980,31 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q13" t="n">
         <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
         <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
         <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
         <v>1.22</v>
@@ -2019,13 +2019,13 @@
         <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD13" t="n">
         <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.3</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>3.19</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.53</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.3</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="O16" t="n">
-        <v>2.94</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>3.12</v>
+        <v>2.41</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.49</v>
+        <v>3.94</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,70 +2444,70 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.33</v>
+        <v>4.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
         <v>1.91</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.34</v>
+        <v>2.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.94</v>
+        <v>2.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.51</v>
+        <v>2.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.3</v>
+        <v>2.41</v>
       </c>
       <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.45</v>
       </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.46</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.49</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.73</v>
+        <v>2.61</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.96</v>
+        <v>3.24</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.38</v>
+        <v>2.91</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.02</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
         <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.8</v>
@@ -3572,16 +3572,16 @@
         <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>3.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>6.25</v>
+        <v>7.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.61</v>
+        <v>1.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.42</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>2.61</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
         <v>2.04</v>
@@ -680,16 +680,16 @@
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="T2" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -704,16 +704,16 @@
         <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
         <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
         <v>1.82</v>
@@ -725,7 +725,7 @@
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1733,16 +1733,16 @@
         <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="Q11" t="n">
         <v>4.27</v>
@@ -1751,22 +1751,22 @@
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
         <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.12</v>
@@ -1775,28 +1775,28 @@
         <v>4.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AG11" t="n">
         <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="n">
-        <v>2.92</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.37</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.68</v>
-      </c>
-      <c r="O13" t="n">
-        <v>5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.6</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>2.61</v>
       </c>
       <c r="O15" t="n">
-        <v>2.15</v>
+        <v>3.04</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>3.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
         <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
         <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="AD15" t="n">
         <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.68</v>
+        <v>3.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.73</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.96</v>
+        <v>5.17</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.36</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.91</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AG18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.3</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.47</v>
+        <v>6.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>2.64</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.5</v>
+        <v>3.67</v>
       </c>
       <c r="R20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.3</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z20" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.69</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.18</v>
+        <v>2.14</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.94</v>
+        <v>3.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.37</v>
+        <v>2.69</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.81</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>2.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.67</v>
+        <v>3.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.24</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.67</v>
+        <v>5.11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,19 +3396,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.87</v>
+        <v>4.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="O25" t="n">
         <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
         <v>2.28</v>
@@ -3420,16 +3420,16 @@
         <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3438,25 +3438,25 @@
         <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
         <v>1.26</v>
@@ -3515,40 +3515,40 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q26" t="n">
         <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -3569,7 +3569,7 @@
         <v>2.34</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE26" t="n">
         <v>1.79</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="P27" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>4.06</v>
       </c>
       <c r="R27" t="n">
         <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
         <v>3.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD27" t="n">
         <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.03</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>6.36</v>
       </c>
       <c r="O28" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="R28" t="n">
         <v>1.41</v>
@@ -3777,40 +3777,40 @@
         <v>2.89</v>
       </c>
       <c r="T28" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
         <v>7.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
         <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD28" t="n">
         <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AF28" t="n">
         <v>1.75</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.13</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>2.13</v>
+        <v>2.92</v>
       </c>
       <c r="P11" t="n">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.27</v>
+        <v>3.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>8.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.33</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.46</v>
+        <v>3.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.31</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>3.26</v>
+        <v>5.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
         <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.13</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.92</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.93</v>
+        <v>4.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>2.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.95</v>
+        <v>2.46</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="O14" t="n">
-        <v>5.2</v>
+        <v>3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
         <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.61</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>3.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.24</v>
+        <v>2.47</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.91</v>
+        <v>2.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.24</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.42</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.42</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.17</v>
+        <v>6.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.63</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
         <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.47</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.28</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>3.67</v>
       </c>
       <c r="R19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z19" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.67</v>
+        <v>2.81</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.39</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>2.61</v>
       </c>
       <c r="O21" t="n">
-        <v>2.14</v>
+        <v>3.04</v>
       </c>
       <c r="P21" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.5</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
         <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>5.11</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
         <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.62</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.3</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.67</v>
+        <v>3.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="O24" t="n">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.11</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
         <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,37 +3634,37 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>4.03</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>6.36</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>2.07</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.06</v>
+        <v>6.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="W27" t="n">
         <v>1.08</v>
@@ -3673,34 +3673,34 @@
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>2.61</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,37 +3753,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.03</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.36</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.07</v>
+        <v>2.79</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.4</v>
+        <v>4.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
         <v>1.08</v>
@@ -3792,34 +3792,34 @@
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.61</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1141,7 +1141,7 @@
         <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1730,31 +1730,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
         <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
         <v>1.35</v>
@@ -1763,40 +1763,40 @@
         <v>8.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
         <v>3.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF11" t="n">
         <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
         <v>2.67</v>
@@ -1885,7 +1885,7 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.22</v>
@@ -1894,10 +1894,10 @@
         <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
         <v>2.9</v>
@@ -1971,70 +1971,70 @@
         <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>2.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
         <v>4.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V13" t="n">
         <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
         <v>2.6</v>
@@ -2132,7 +2132,7 @@
         <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
         <v>2.1</v>
@@ -2150,7 +2150,7 @@
         <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
         <v>1.39</v>
@@ -2209,13 +2209,13 @@
         <v>3.3</v>
       </c>
       <c r="M15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.9</v>
       </c>
       <c r="P15" t="n">
         <v>2.4</v>
@@ -2227,40 +2227,40 @@
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
         <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
         <v>1.56</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>2.14</v>
+        <v>3.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V16" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.5</v>
+        <v>6.58</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
@@ -2468,7 +2468,7 @@
         <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U17" t="n">
         <v>1.44</v>
@@ -2483,28 +2483,28 @@
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG17" t="n">
         <v>1.14</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>3.73</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>2.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>4.96</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB18" t="n">
         <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.8</v>
+        <v>3.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.9</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
@@ -2724,13 +2724,13 @@
         <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
         <v>3.42</v>
@@ -2739,16 +2739,16 @@
         <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
         <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>3.18</v>
@@ -2819,7 +2819,7 @@
         <v>2.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
         <v>3.18</v>
@@ -2828,7 +2828,7 @@
         <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
         <v>5.2</v>
@@ -2846,10 +2846,10 @@
         <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
         <v>2.67</v>
@@ -2920,28 +2920,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="P21" t="n">
         <v>2.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
         <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="T21" t="n">
         <v>2.56</v>
@@ -2953,10 +2953,10 @@
         <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
         <v>1.19</v>
@@ -2965,10 +2965,10 @@
         <v>3.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>2.91</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>3.52</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.11</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.17</v>
+        <v>5.27</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
@@ -3197,34 +3197,34 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
         <v>3.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
         <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="P24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V24" t="n">
-        <v>9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.78</v>
+        <v>2.94</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.42</v>
+        <v>2.28</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.7</v>
+        <v>3.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="N25" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
@@ -3420,10 +3420,10 @@
         <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
         <v>6</v>
@@ -3432,37 +3432,37 @@
         <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
         <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3634,43 +3634,43 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6.36</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="P27" t="n">
         <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="T27" t="n">
         <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
         <v>1.26</v>
@@ -3679,28 +3679,28 @@
         <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.99</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>5.15</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>3.99</v>
       </c>
       <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.36</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2.13</v>
+        <v>5.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.27</v>
+        <v>2.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="U13" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.39</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.72</v>
+        <v>2.13</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>4.27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="V14" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>2.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.47</v>
+        <v>3.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
         <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.49</v>
+        <v>2.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.24</v>
+        <v>2.33</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>5.27</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="AD16" t="n">
         <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6.1</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.9</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.73</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>2.42</v>
+        <v>3.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.96</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>2.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>4.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.58</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>1.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.81</v>
+        <v>6.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.65</v>
+        <v>3.73</v>
       </c>
       <c r="O21" t="n">
-        <v>2.97</v>
+        <v>2.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>4.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.74</v>
+        <v>3.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>2.81</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.03</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.57</v>
+        <v>2.67</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>2.61</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="O23" t="n">
-        <v>2.33</v>
+        <v>3.52</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.27</v>
+        <v>3.24</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.63</v>
+        <v>3.57</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.92</v>
+        <v>1.42</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.02</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q27" t="n">
-        <v>6.7</v>
+        <v>4.06</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.79</v>
+        <v>2.02</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.06</v>
+        <v>6.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -662,7 +662,7 @@
         <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
         <v>3.45</v>
@@ -671,7 +671,7 @@
         <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
         <v>3.99</v>
@@ -680,13 +680,13 @@
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
         <v>7.5</v>
@@ -698,34 +698,34 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
         <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
         <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.8</v>
+        <v>6.99</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1620,64 +1620,64 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.52</v>
+        <v>4.09</v>
       </c>
       <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.36</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
         <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
         <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
         <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.99</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>8.1</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.41</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>5.15</v>
+        <v>3.74</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
         <v>4</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.27</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.6</v>
+        <v>3.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>3.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.39</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.28</v>
+        <v>4.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.21</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>3.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.91</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.27</v>
+        <v>3.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.04</v>
+        <v>3.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>5.27</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -2471,46 +2471,46 @@
         <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>3.73</v>
       </c>
       <c r="O18" t="n">
-        <v>3.24</v>
+        <v>2.42</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
         <v>1.71</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.3</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="AA19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.58</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.3</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="Z20" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>3.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.64</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.12</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.73</v>
+        <v>6.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.96</v>
+        <v>6.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="T21" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.04</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.93</v>
+        <v>2.64</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
         <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.81</v>
+        <v>5.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.12</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.24</v>
+        <v>2.39</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.03</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.57</v>
+        <v>2.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
         <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.36</v>
       </c>
-      <c r="Q24" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.51</v>
+        <v>4.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.94</v>
+        <v>2.49</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3405,13 +3405,13 @@
         <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
@@ -3420,19 +3420,19 @@
         <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
         <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="W25" t="n">
         <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1.21</v>
@@ -3447,22 +3447,22 @@
         <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="P26" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.48</v>
+        <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>7.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>1.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.06</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>3.44</v>
       </c>
       <c r="T27" t="n">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>5.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.14</v>
+        <v>4.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.42</v>
+        <v>2.47</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>3.28</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.02</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q28" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.78</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4.7</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>6.45</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>2.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="N12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>2.76</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>3.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>3.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="P14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.06</v>
+        <v>3.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>3.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2.97</v>
+        <v>2.42</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.24</v>
+        <v>4.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.09</v>
@@ -2364,34 +2364,34 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.27</v>
+        <v>4.06</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
         <v>2.9</v>
       </c>
       <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>5.27</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.38</v>
+        <v>2.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="M20" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.57</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.86</v>
+        <v>5.2</v>
       </c>
       <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.39</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.28</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
         <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.39</v>
+        <v>6.86</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>2.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.81</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>7.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>2.93</v>
+        <v>3.44</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.33</v>
       </c>
-      <c r="M27" t="n">
-        <v>5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="AH27" t="n">
         <v>1.64</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>3.28</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="M2" t="n">
         <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
         <v>2.38</v>
@@ -704,7 +704,7 @@
         <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB2" t="n">
         <v>1.8</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.4</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.24</v>
+        <v>2.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.87</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.91</v>
+        <v>2.49</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>5.27</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.06</v>
+        <v>6.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.36</v>
       </c>
-      <c r="V17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q18" t="n">
-        <v>5.27</v>
+        <v>2.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.13</v>
+        <v>4.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.81</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.12</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.39</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>2.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N21" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q21" t="n">
         <v>4.8</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.2</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.09</v>
@@ -2959,34 +2959,34 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.28</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>2.41</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>6.1</v>
+        <v>2.69</v>
       </c>
       <c r="O23" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.86</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.3</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.64</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>4.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
         <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH27" t="n">
         <v>2.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.33</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1528,7 +1528,7 @@
         <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.26</v>
@@ -1558,7 +1558,7 @@
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.71</v>
+        <v>5.66</v>
       </c>
       <c r="N10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.25</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.41</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="P12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.85</v>
+        <v>3.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.85</v>
+        <v>3.74</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4.7</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45</v>
+        <v>4.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>2.41</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="O15" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>2.94</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.49</v>
+        <v>3.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.27</v>
+        <v>3.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="V16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,49 +2444,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>6.1</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>2.97</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.86</v>
+        <v>3.24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
         <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="AA17" t="n">
         <v>1.8</v>
@@ -2495,22 +2495,22 @@
         <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.64</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.35</v>
+        <v>3.73</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.81</v>
+        <v>4.25</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.28</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.99</v>
+        <v>3.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.87</v>
+        <v>3.12</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.91</v>
+        <v>3.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.73</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.42</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.8</v>
+        <v>2.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.44</v>
       </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>6.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>6.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.35</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.3</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.12</v>
-      </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3405,13 +3405,13 @@
         <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P25" t="n">
         <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
@@ -3435,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
         <v>3.62</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
         <v>2.05</v>
@@ -1510,55 +1510,55 @@
         <v>4.09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
         <v>2.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
         <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
         <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
         <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1617,7 +1617,7 @@
         <v>5.66</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>4.7</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>6.45</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1977,7 +1977,7 @@
         <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1989,13 +1989,13 @@
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>8.5</v>
@@ -2004,7 +2004,7 @@
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.36</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>3.74</v>
       </c>
       <c r="P14" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.25</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH14" t="n">
-        <v>2.41</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.94</v>
+        <v>3.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.57</v>
+        <v>2.91</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.42</v>
+        <v>4.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.24</v>
+        <v>2.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.42</v>
       </c>
-      <c r="V17" t="n">
-        <v>6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.73</v>
+        <v>2.71</v>
       </c>
       <c r="O18" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
         <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.05</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>2.83</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>6.1</v>
+        <v>2.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.85</v>
+        <v>3.54</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.86</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>6.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.81</v>
+        <v>6.86</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,67 +3396,67 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
         <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
         <v>5.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
         <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AG25" t="n">
         <v>1.25</v>
@@ -3521,7 +3521,7 @@
         <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.75</v>
@@ -3539,13 +3539,13 @@
         <v>3.44</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.14</v>
@@ -3557,31 +3557,31 @@
         <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG26" t="n">
         <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3643,7 +3643,7 @@
         <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="P27" t="n">
         <v>2.3</v>
@@ -3661,10 +3661,10 @@
         <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
@@ -3685,22 +3685,22 @@
         <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
         <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
         <v>3</v>
@@ -3798,7 +3798,7 @@
         <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
         <v>1.75</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -716,16 +716,16 @@
         <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
         <v>2.55</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4.7</v>
+        <v>3.72</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
         <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>4.92</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.25</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>2.84</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.44</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.57</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>4.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.11</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.74</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.74</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>2.97</v>
@@ -2251,19 +2251,19 @@
         <v>3.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC15" t="n">
         <v>2.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>2.18</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.05</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.81</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.28</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O18" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.42</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.4</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.63</v>
+        <v>2.99</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="O20" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.65</v>
+        <v>5.27</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>5.25</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>3.98</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.28</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.83</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>3.54</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>6.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.89</v>
+        <v>3.74</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.72</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>2.62</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.86</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.64</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M24" t="n">
         <v>3.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
         <v>5</v>
@@ -3536,13 +3536,13 @@
         <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
         <v>5.3</v>
@@ -3563,10 +3563,10 @@
         <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
@@ -3637,10 +3637,10 @@
         <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="O27" t="n">
         <v>1.99</v>
@@ -3661,7 +3661,7 @@
         <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
         <v>6.4</v>
@@ -3679,16 +3679,16 @@
         <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
         <v>2.04</v>
@@ -3700,7 +3700,7 @@
         <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>5.58</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.72</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>2.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.92</v>
+        <v>2.16</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>2.81</v>
       </c>
       <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="AB12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.33</v>
       </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>4.92</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.25</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.41</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.81</v>
+        <v>3.72</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.17</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.27</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.24</v>
+        <v>4.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
@@ -2245,34 +2245,34 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.85</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC16" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
         <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O17" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.42</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>6.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>3.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.29</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>3.98</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.27</v>
+        <v>2.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.92</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M21" t="n">
         <v>3.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.6</v>
-      </c>
       <c r="N21" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.88</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.42</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
       </c>
       <c r="V22" t="n">
         <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.74</v>
+        <v>3.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.64</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.3</v>
       </c>
-      <c r="N24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF24" t="n">
         <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
         <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.33</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.07</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.4</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC28" t="n">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>3.32</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2.81</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>2.57</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>3.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.43</v>
+        <v>3.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.17</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
         <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -2010,16 +2010,16 @@
         <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.74</v>
+        <v>4.09</v>
       </c>
       <c r="AA13" t="n">
         <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
         <v>1.36</v>
@@ -2031,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="n">
         <v>1.17</v>
@@ -2087,25 +2087,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
         <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
         <v>3.12</v>
@@ -2114,13 +2114,13 @@
         <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
         <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
@@ -2132,19 +2132,19 @@
         <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>2.15</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
@@ -2245,34 +2245,34 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="AD15" t="n">
         <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.71</v>
+        <v>3.73</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.89</v>
+        <v>4.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.72</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.42</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.53</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.74</v>
+        <v>3.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>3.98</v>
+        <v>2.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.39</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>2.3</v>
@@ -2962,31 +2962,31 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
         <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
         <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.97</v>
+        <v>1.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>6.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
         <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>2.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O23" t="n">
         <v>2.62</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.1</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
         <v>3.9</v>
       </c>
-      <c r="N24" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.28</v>
+        <v>1.16</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="N25" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="O25" t="n">
         <v>4.4</v>
@@ -3411,13 +3411,13 @@
         <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
         <v>2.4</v>
@@ -3438,25 +3438,25 @@
         <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>2.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AG25" t="n">
         <v>1.25</v>
@@ -3518,13 +3518,13 @@
         <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="P26" t="n">
         <v>2.3</v>
@@ -3536,7 +3536,7 @@
         <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
         <v>2.6</v>
@@ -3560,10 +3560,10 @@
         <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>3.08</v>
@@ -3578,10 +3578,10 @@
         <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="T27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB27" t="n">
         <v>2.4</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC27" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>3.32</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.34</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.75</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="AC28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.64</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3.32</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.18</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.05</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.41</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z13" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>2.57</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.28</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.73</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.42</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.85</v>
+        <v>3.38</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.81</v>
+        <v>2.94</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>6.1</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.86</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.53</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.82</v>
+        <v>2.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>6.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>6.86</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.95</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.33</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.88</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.02</v>
       </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>2.88</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>2.38</v>
@@ -683,7 +683,7 @@
         <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
         <v>1.34</v>
@@ -698,16 +698,16 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC2" t="n">
         <v>3.28</v>
@@ -716,7 +716,7 @@
         <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
@@ -787,40 +787,40 @@
         <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
@@ -829,22 +829,22 @@
         <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46021.29166666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.28</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>3.78</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.41</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1861,25 +1861,25 @@
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V12" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.08</v>
@@ -1891,7 +1891,7 @@
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
         <v>1.77</v>
@@ -1903,19 +1903,19 @@
         <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.81</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.5</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.05</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.73</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.99</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
         <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.49</v>
+        <v>2.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>2.31</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>3.98</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.38</v>
+        <v>3.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.42</v>
       </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.27</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
         <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.56</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>1.42</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.86</v>
+        <v>5.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.82</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>3.04</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.55</v>
+        <v>3.87</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3408,7 +3408,7 @@
         <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="Q25" t="n">
         <v>2.4</v>
@@ -3423,7 +3423,7 @@
         <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
         <v>5.6</v>
@@ -3432,7 +3432,7 @@
         <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1.22</v>
@@ -3459,10 +3459,10 @@
         <v>2.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.02</v>
       </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AD26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>2.9</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3637,10 +3637,10 @@
         <v>1.34</v>
       </c>
       <c r="M27" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="O27" t="n">
         <v>1.75</v>
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
         <v>2.36</v>
@@ -3679,28 +3679,28 @@
         <v>4.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
         <v>2.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AF27" t="n">
         <v>1.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.95</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.28</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.34</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.88</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.61</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.88</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.53</v>
-      </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>3.98</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.38</v>
+        <v>3.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.31</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M19" t="n">
         <v>3.3</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
         <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.81</v>
+        <v>5.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>2.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>2.31</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>6.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>6.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.86</v>
+        <v>5.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.64</v>
+        <v>1.95</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="O23" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.38</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.04</v>
+        <v>3.87</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.42</v>
       </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -662,25 +662,25 @@
         <v>1.99</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
         <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
         <v>2.83</v>
@@ -698,13 +698,13 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB2" t="n">
         <v>1.76</v>
@@ -725,7 +725,7 @@
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.54</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.06</v>
+        <v>3.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.84</v>
+        <v>2.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2248,31 +2248,31 @@
         <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.98</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
         <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>3.73</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.03</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.98</v>
+        <v>3.04</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.39</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.47</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.62</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
       </c>
       <c r="T19" t="n">
         <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.2</v>
+        <v>6.86</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
         <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>4.3</v>
+        <v>3.12</v>
       </c>
       <c r="N21" t="n">
-        <v>6.1</v>
+        <v>3.73</v>
       </c>
       <c r="O21" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="P21" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.86</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.78</v>
+        <v>3.03</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.92</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.64</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.38</v>
+        <v>5.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.62</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.04</v>
+        <v>3.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O23" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.04</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.87</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.91</v>
+        <v>3.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.81</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.48</v>
+        <v>4.45</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.45</v>
+        <v>3.48</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>3.48</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.06</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
         <v>5.5</v>
@@ -2364,34 +2364,34 @@
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.39</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>3.73</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.81</v>
+        <v>3.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>3.03</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>1.92</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,70 +2563,70 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.87</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
         <v>1.47</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
         <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>3.98</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.38</v>
+        <v>2.39</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.04</v>
+        <v>3.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.73</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>5.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T21" t="n">
         <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
         <v>1.09</v>
@@ -2959,34 +2959,34 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,70 +3277,70 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.38</v>
       </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
         <v>1.47</v>
@@ -3753,25 +3753,25 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
         <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
         <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>2.8</v>
@@ -3786,40 +3786,40 @@
         <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
         <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="N3" t="n">
         <v>2.55</v>
@@ -826,7 +826,7 @@
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
         <v>5.85</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="AA11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.34</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1864,7 +1864,7 @@
         <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -1873,25 +1873,25 @@
         <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA12" t="n">
         <v>1.73</v>
@@ -1912,10 +1912,10 @@
         <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -2001,7 +2001,7 @@
         <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
@@ -2019,22 +2019,22 @@
         <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AF13" t="n">
         <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2.43</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.05</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>3.73</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.81</v>
+        <v>3.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>6.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.49</v>
+        <v>3.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>3.73</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.66</v>
+        <v>4.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
         <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.92</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2620,7 +2620,7 @@
         <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
         <v>2</v>
@@ -2629,7 +2629,7 @@
         <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2694,25 +2694,25 @@
         <v>3.98</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
         <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="U19" t="n">
         <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.11</v>
@@ -2721,7 +2721,7 @@
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
         <v>3.88</v>
@@ -2739,10 +2739,10 @@
         <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AG19" t="n">
         <v>1.21</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.86</v>
+        <v>2.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.42</v>
       </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.64</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="P21" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
         <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
         <v>1.09</v>
@@ -2959,34 +2959,34 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.31</v>
+        <v>1.47</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.38</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U22" t="n">
         <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3176,31 +3176,31 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
         <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="AA23" t="n">
         <v>2.17</v>
@@ -3209,19 +3209,19 @@
         <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="AD23" t="n">
         <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH23" t="n">
         <v>1.4</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>4.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.87</v>
+        <v>2.97</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.91</v>
+        <v>3.79</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3405,40 +3405,40 @@
         <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="AA25" t="n">
         <v>1.77</v>
@@ -3447,19 +3447,19 @@
         <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.73</v>
+        <v>2.08</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="n">
         <v>1.18</v>
@@ -3518,10 +3518,10 @@
         <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="N26" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.75</v>
@@ -3536,19 +3536,19 @@
         <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
@@ -3557,25 +3557,25 @@
         <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AC26" t="n">
         <v>2.49</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
         <v>1.92</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG26" t="n">
         <v>1.19</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.95</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.05</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>2.04</v>
       </c>
       <c r="P28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="W28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.02</v>
       </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>3.44</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
         <v>3.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="T3" t="n">
         <v>3.92</v>
@@ -808,28 +808,28 @@
         <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AB3" t="n">
         <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="AD3" t="n">
         <v>1.07</v>
@@ -838,13 +838,13 @@
         <v>2.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46021.29166666666</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
@@ -1159,10 +1159,10 @@
         <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>6.5</v>
       </c>
       <c r="P9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF9" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.5</v>
+        <v>2.56</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1730,55 +1730,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>2.88</v>
@@ -1787,16 +1787,16 @@
         <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
         <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>5.86</v>
       </c>
       <c r="O12" t="n">
-        <v>3.78</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>5.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="T12" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1998,7 +1998,7 @@
         <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
@@ -2010,13 +2010,13 @@
         <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
         <v>3.74</v>
@@ -2031,7 +2031,7 @@
         <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
         <v>1.75</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3.82</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.43</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.66</v>
+        <v>4.96</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>6.65</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.03</v>
+        <v>3.79</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.59</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
         <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.72</v>
+        <v>2.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>4.72</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>3.98</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC19" t="n">
         <v>3.88</v>
       </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
@@ -2840,34 +2840,34 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.05</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
         <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
         <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="O24" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.96</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.33</v>
       </c>
-      <c r="V24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -3533,13 +3533,13 @@
         <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="U26" t="n">
         <v>1.58</v>
@@ -3557,16 +3557,16 @@
         <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA26" t="n">
         <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
@@ -3581,7 +3581,7 @@
         <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3634,37 +3634,37 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
         <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>4.04</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="W27" t="n">
         <v>1.02</v>
@@ -3676,13 +3676,13 @@
         <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
         <v>3.42</v>
@@ -3753,16 +3753,16 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
@@ -3771,10 +3771,10 @@
         <v>5.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="T28" t="n">
         <v>2.7</v>
@@ -3783,7 +3783,7 @@
         <v>1.41</v>
       </c>
       <c r="V28" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="W28" t="n">
         <v>1.06</v>
@@ -3795,13 +3795,13 @@
         <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
         <v>3.12</v>
@@ -3810,16 +3810,16 @@
         <v>1.31</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="P2" t="n">
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="T2" t="n">
         <v>2.83</v>
@@ -698,13 +698,13 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB2" t="n">
         <v>1.76</v>
@@ -716,7 +716,7 @@
         <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
@@ -725,7 +725,7 @@
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.45</v>
       </c>
       <c r="O3" t="n">
         <v>4.15</v>
@@ -817,16 +817,16 @@
         <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
         <v>5.8</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.28</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4.33</v>
+        <v>2.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1052,37 +1052,37 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>3.09</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2.32</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.34</v>
+        <v>2.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>2.5</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.3</v>
       </c>
-      <c r="O9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.56</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.11</v>
+        <v>6.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.25</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.07</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.07</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="N15" t="n">
-        <v>6.1</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.91</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
         <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.64</v>
+        <v>1.48</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.96</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="T16" t="n">
         <v>2.9</v>
@@ -2355,43 +2355,43 @@
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.79</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>3.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
         <v>2.05</v>
@@ -2578,7 +2578,7 @@
         <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.72</v>
+        <v>5.72</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
@@ -2587,10 +2587,10 @@
         <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
         <v>6.05</v>
@@ -2602,16 +2602,16 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>2.85</v>
@@ -2620,10 +2620,10 @@
         <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AG18" t="n">
         <v>1.23</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.22</v>
+        <v>2.59</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.88</v>
+        <v>3.79</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M20" t="n">
         <v>3.3</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.98</v>
+        <v>2.98</v>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="T20" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="O21" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
         <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.73</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>6.65</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.03</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>6.91</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>2.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.41</v>
+        <v>1.74</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="O25" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
         <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
         <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.25</v>
+        <v>5.16</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.17</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
-        <v>3.26</v>
+        <v>4.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.26</v>
+        <v>7.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.04</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>2.66</v>
+        <v>3.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="V27" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>4.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>2.39</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.42</v>
+        <v>2.52</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>3.28</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.26</v>
       </c>
       <c r="N28" t="n">
-        <v>6.5</v>
+        <v>3.26</v>
       </c>
       <c r="O28" t="n">
-        <v>2.02</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.8</v>
+        <v>4.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.55</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1052,37 +1052,37 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.56</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.11</v>
+        <v>6.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.3</v>
       </c>
-      <c r="O10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.86</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.6</v>
       </c>
-      <c r="O13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.52</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.2</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
         <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="M17" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.2</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>2.59</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.72</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.36</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V18" t="n">
-        <v>6.05</v>
+        <v>7.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.44</v>
+        <v>2.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.85</v>
+        <v>3.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.84</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.59</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>6.91</v>
       </c>
       <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.42</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.5</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.92</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.1</v>
+        <v>2.05</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>5.72</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>2.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.91</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.64</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O24" t="n">
         <v>4.1</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U24" t="n">
         <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD24" t="n">
         <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
         <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3753,19 +3753,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>4.04</v>
@@ -3774,16 +3774,16 @@
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
         <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
         <v>1.02</v>
@@ -3795,13 +3795,13 @@
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>3.42</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2.31</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1052,37 +1052,37 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.09</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.3</v>
       </c>
-      <c r="O9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.56</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.11</v>
+        <v>6.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>5.86</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.07</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.74</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.86</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q12" t="n">
-        <v>5.35</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>3.38</v>
+        <v>2.54</v>
       </c>
       <c r="T12" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>3.07</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>3.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.6</v>
       </c>
-      <c r="O14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
         <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
         <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.22</v>
+        <v>2.58</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>4.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
         <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>6.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="T17" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD17" t="n">
         <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>2.64</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.25</v>
       </c>
-      <c r="N18" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O18" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.79</v>
+        <v>3.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>4.25</v>
+        <v>3.12</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>3.73</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.91</v>
+        <v>3.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W19" t="n">
         <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
         <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>5.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.46</v>
+        <v>2.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.05</v>
+        <v>4.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.72</v>
+        <v>2.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.44</v>
+        <v>3.71</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.45</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.49</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>2.61</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="P24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="AB24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="N25" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="P25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.32</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V25" t="n">
         <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3438,28 +3438,28 @@
         <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.16</v>
+        <v>4.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="n">
         <v>1.17</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.8</v>
+        <v>4.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.55</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="M27" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="T27" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>7.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.04</v>
+        <v>8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH28" t="n">
         <v>3.28</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>4.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.38</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
         <v>9.9</v>
@@ -814,19 +814,19 @@
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
         <v>5.8</v>
@@ -835,16 +835,16 @@
         <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46021.29166666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="M4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.7</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46021.375</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
         <v>4.33</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1263,64 +1263,64 @@
         <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46021.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>5.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>5.86</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.35</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.46</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>5.86</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.07</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.74</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.6</v>
       </c>
-      <c r="O13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.36</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z14" t="n">
-        <v>3.9</v>
+        <v>3.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.85</v>
+        <v>3.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.58</v>
+        <v>4.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.85</v>
+        <v>2.39</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>3.71</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.92</v>
+        <v>2.58</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.86</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.83</v>
+        <v>3.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.64</v>
+        <v>1.79</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.05</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.73</v>
+        <v>2.69</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
         <v>3.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.68</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="U20" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.44</v>
+        <v>2.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>3.62</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.33</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.3</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>4.18</v>
+        <v>2.05</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.39</v>
+        <v>5.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.35</v>
+        <v>6.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.81</v>
+        <v>6.86</v>
       </c>
       <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O24" t="n">
         <v>2.61</v>
       </c>
-      <c r="M24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.18</v>
-      </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.26</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U24" t="n">
         <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
         <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
         <v>1.88</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>7.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.04</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH26" t="n">
         <v>3.28</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>7.75</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>4.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.38</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.64</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3.28</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="M2" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="O2" t="n">
         <v>2.48</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.07</v>
+        <v>3.62</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -683,13 +683,13 @@
         <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -698,34 +698,34 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46021.22916666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O3" t="n">
         <v>4.46</v>
@@ -817,16 +817,16 @@
         <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
         <v>5.8</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>3.72</v>
@@ -936,16 +936,16 @@
         <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
         <v>5.3</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA5" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2.31</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1293,16 +1293,16 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
         <v>4.1</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="N8" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.9</v>
@@ -1492,55 +1492,55 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.56</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.59</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
         <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
         <v>3.5</v>
@@ -1549,16 +1549,16 @@
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>6.07</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
         <v>6.5</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
         <v>1.86</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>3.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.86</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.35</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.46</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3.82</v>
+        <v>5.4</v>
       </c>
       <c r="P13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.07</v>
+        <v>5.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>2.56</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.98</v>
+        <v>4.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
@@ -2230,49 +2230,49 @@
         <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
         <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4.18</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.71</v>
+        <v>4.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
         <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.85</v>
+        <v>4.26</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.85</v>
+        <v>3.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>3.73</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.66</v>
+        <v>5.72</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
         <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.07</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>2.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N19" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.68</v>
+        <v>3.36</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="U21" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V21" t="n">
-        <v>6.05</v>
+        <v>6.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
         <v>3.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="AD21" t="n">
         <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>2.57</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.86</v>
+        <v>4.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.83</v>
+        <v>3.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.64</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>6.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.18</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.81</v>
+        <v>6.81</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.18</v>
+        <v>2.91</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="O24" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.26</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3405,40 +3405,40 @@
         <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="P25" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="Q25" t="n">
         <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
         <v>1.77</v>
@@ -3453,16 +3453,16 @@
         <v>1.66</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AG25" t="n">
         <v>2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>7.75</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>4.04</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.27</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z26" t="n">
-        <v>4.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.64</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>3.28</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.8</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
         <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.04</v>
+        <v>6.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="T28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.4</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC28" t="n">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>3.19</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>5.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>2.56</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.55</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>2.24</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>3.84</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.25</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>6.81</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
@@ -2236,43 +2236,43 @@
         <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>2.57</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.81</v>
+        <v>4.8</v>
       </c>
       <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.28</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z16" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.49</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.25</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.26</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="T17" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.13</v>
+        <v>4.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.72</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
         <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.17</v>
+        <v>2.74</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>4.26</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U19" t="n">
         <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.93</v>
+        <v>3.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N21" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.69</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.77</v>
-      </c>
       <c r="U21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.39</v>
       </c>
-      <c r="V21" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AE21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.8</v>
+        <v>5.72</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.33</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>2.41</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>6.1</v>
+        <v>2.69</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.81</v>
+        <v>3.36</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="T23" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>2.61</v>
       </c>
       <c r="M24" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="N24" t="n">
-        <v>3.73</v>
+        <v>2.56</v>
       </c>
       <c r="O24" t="n">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.85</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="T24" t="n">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.92</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
+        <v>8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q27" t="n">
         <v>6.9</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.13</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="V27" t="n">
-        <v>6.2</v>
+        <v>5.15</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.02</v>
+        <v>5.2</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="P28" t="n">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.9</v>
+        <v>5.13</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>5.15</v>
+        <v>6.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.2</v>
+        <v>4.02</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>4.46</v>
+        <v>4.25</v>
       </c>
       <c r="P3" t="n">
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
         <v>1.65</v>
@@ -817,16 +817,16 @@
         <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
         <v>5.8</v>
@@ -835,16 +835,16 @@
         <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
         <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46021.29166666666</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="P4" t="n">
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="R4" t="n">
         <v>1.63</v>
@@ -936,16 +936,16 @@
         <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>5.3</v>
@@ -963,7 +963,7 @@
         <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46021.375</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>4.86</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46021.41666666666</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
         <v>2.26</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
         <v>11</v>
@@ -1290,28 +1290,28 @@
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AF7" t="n">
         <v>1.55</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.55</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>3.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>3.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.55</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>5.4</v>
+        <v>2.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>5.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>2.67</v>
+        <v>2.24</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.74</v>
+        <v>5.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.33</v>
       </c>
-      <c r="V14" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AH14" t="n">
         <v>1.37</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.45</v>
       </c>
-      <c r="M15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.57</v>
+        <v>4.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="O18" t="n">
-        <v>4.25</v>
+        <v>3.17</v>
       </c>
       <c r="P18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AB18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
         <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
         <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.18</v>
+        <v>2.13</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.81</v>
+        <v>5.72</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC21" t="n">
         <v>3.12</v>
       </c>
-      <c r="N21" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.06</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.13</v>
+        <v>2.74</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.72</v>
+        <v>4.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N23" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.69</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.77</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.39</v>
       </c>
-      <c r="V23" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AE23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.88</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.93</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.04</v>
+        <v>6.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="V26" t="n">
-        <v>7.7</v>
+        <v>5.15</v>
       </c>
       <c r="W26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.02</v>
       </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.14</v>
+        <v>5.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>3.19</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="P27" t="n">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.9</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="T27" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>5.15</v>
+        <v>6.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.2</v>
+        <v>4.02</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.13</v>
+        <v>4.04</v>
       </c>
       <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.34</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.47</v>
-      </c>
       <c r="V28" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.02</v>
+        <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.66</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -764,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,80 +893,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>2.58</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.55</v>
+        <v>2.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.62</v>
+        <v>6.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="U4" t="n">
         <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46021.375</v>
+        <v>46021.35416666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,102 +990,102 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
         <v>5.3</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V5" t="n">
-        <v>8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AF5" t="n">
         <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46021.41666666666</v>
+        <v>46021.375</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.69</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>2.51</v>
@@ -1293,16 +1293,16 @@
         <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
         <v>4.4</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>3.54</v>
       </c>
       <c r="T11" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
-        <v>8.300000000000001</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.6</v>
+        <v>2.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>4.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.56</v>
+        <v>1.74</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>6.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.49</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O16" t="n">
         <v>3.3</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AB16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="AH16" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.25</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.88</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.93</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.8</v>
+        <v>3.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.73</v>
       </c>
       <c r="O20" t="n">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.72</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
         <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.41</v>
       </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q21" t="n">
-        <v>3.36</v>
+        <v>5.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>6.95</v>
+        <v>6.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
         <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.26</v>
+        <v>2.53</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="T22" t="n">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>3.73</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AC23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.92</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.1</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.81</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.33</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3405,40 +3405,40 @@
         <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>4.41</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
         <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="V25" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
         <v>1.77</v>
@@ -3453,16 +3453,16 @@
         <v>1.66</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG25" t="n">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.9</v>
+        <v>4.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.38</v>
+        <v>2.69</v>
       </c>
       <c r="T26" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>5.15</v>
+        <v>7.7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.19</v>
+        <v>1.65</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="N27" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="P27" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="V27" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.02</v>
+        <v>4.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.3</v>
       </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.69</v>
-      </c>
       <c r="T28" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>4.02</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>2.88</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1250,32 +1250,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="O7" t="n">
         <v>2.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T7" t="n">
         <v>3.58</v>
@@ -1293,34 +1293,34 @@
         <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
         <v>2.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG7" t="n">
         <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46021.5</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V8" t="n">
         <v>6.7</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46021.52083333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.26</v>
+        <v>6.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.61</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>7.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.34</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>2.97</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V10" t="n">
         <v>9</v>
       </c>
-      <c r="M10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>2.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.86</v>
+        <v>4.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46021.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.35</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.88</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.62</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="N17" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.87</v>
+        <v>2.99</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>2.41</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>6.1</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
         <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.76</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.32</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.56</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.72</v>
+        <v>2.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.73</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
         <v>4</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.17</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.41</v>
-      </c>
       <c r="Q21" t="n">
-        <v>5.25</v>
+        <v>2.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="U21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.53</v>
+        <v>3.56</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
         <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AD22" t="n">
         <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.89</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.28</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.52</v>
+        <v>3.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>7.4</v>
+        <v>6.05</v>
       </c>
       <c r="W24" t="n">
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>5.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.04</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>3.19</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>5.15</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.82</v>
+        <v>2.84</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>4.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>5.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.5</v>
+        <v>3.96</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
         <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.19</v>
+        <v>1.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1356,20 +1356,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1597,17 +1597,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2.01</v>
+        <v>5.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.22</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.55</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V12" t="n">
         <v>5.25</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.45</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.53</v>
@@ -2004,31 +2004,31 @@
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD13" t="n">
         <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
         <v>1.38</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>2.56</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46021.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.65</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="AA15" t="n">
         <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.9</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
         <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.32</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.73</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.54</v>
+        <v>2.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.99</v>
+        <v>3.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
         <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.44</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,70 +2682,70 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
         <v>1.41</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.89</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O21" t="n">
         <v>3.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.53</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.33</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.72</v>
+        <v>4.03</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
         <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AE23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC23" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.77</v>
+        <v>2.47</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="O24" t="n">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.25</v>
+        <v>3.58</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6.05</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.52</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="AD24" t="n">
         <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.87</v>
+        <v>4.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
         <v>4.2</v>
@@ -3411,25 +3411,25 @@
         <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
         <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="U25" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V25" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3438,31 +3438,31 @@
         <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>5.32</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46021.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>5.15</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.82</v>
+        <v>2.84</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>4.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>5.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.5</v>
+        <v>3.96</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
         <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.19</v>
+        <v>1.63</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.84</v>
+        <v>1.84</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.25</v>
+        <v>6.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V27" t="n">
-        <v>8.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.78</v>
+        <v>4.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.96</v>
+        <v>2.53</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="AE27" t="n">
         <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.63</v>
+        <v>3.09</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46021.71875</v>
@@ -3753,19 +3753,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>7.81</v>
       </c>
       <c r="O28" t="n">
         <v>1.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q28" t="n">
         <v>6.25</v>
@@ -3774,7 +3774,7 @@
         <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
         <v>2.45</v>
@@ -3786,40 +3786,40 @@
         <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
         <v>4.02</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AD28" t="n">
         <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG28" t="n">
         <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46021.71875</v>

--- a/jogos_2025-12-30.xlsx
+++ b/jogos_2025-12-30.xlsx
@@ -1704,99 +1704,99 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>2.16</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>5.75</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.49</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>2.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46021.6875</v>
@@ -1823,99 +1823,99 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.16</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.56</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46021.6875</v>
@@ -1942,99 +1942,99 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.16</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.49</v>
+        <v>3.36</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46021.6875</v>
@@ -2070,20 +2070,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
         <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.28</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.85</v>
+        <v>3.41</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.06</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.52</v>
+        <v>3.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2775,99 +2775,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>6.1</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.23</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46021.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,99 +2894,99 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.75</v>
+        <v>2.52</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3013,99 +3013,99 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.03</v>
+        <v>3.44</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>2.89</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3154,44 +3154,44 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.44</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="N23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -3200,31 +3200,31 @@
         <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.41</v>
+        <v>4.03</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.58</v>
+        <v>5.28</v>
       </c>
       <c r="R24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.36</v>
       </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V24" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46021.69791666666</v>
@@ -3379,20 +3379,20 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,99 +3489,99 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.84</v>
+        <v>1.84</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.25</v>
+        <v>6.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="T26" t="n">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V26" t="n">
-        <v>8.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.78</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.42</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.96</v>
+        <v>2.53</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="AE26" t="n">
         <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.63</v>
+        <v>3.09</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46021.71875</v>
@@ -3608,19 +3608,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-   